--- a/output/coefficients/standardized/standardized_OVR.xlsx
+++ b/output/coefficients/standardized/standardized_OVR.xlsx
@@ -460,15 +460,15 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4783288253257217</v>
+        <v>0.4783</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01030794414712172</v>
+        <v>0.0103</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>46.40390154415856</v>
+        <v>46.4039</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -481,19 +481,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1114987810552704</v>
+        <v>0.1115</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004931284352144412</v>
+        <v>0.0049</v>
       </c>
       <c r="D3" t="n">
-        <v>0.241216519582306</v>
+        <v>0.2412</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01066834307278497</v>
+        <v>0.0107</v>
       </c>
       <c r="F3" t="n">
-        <v>22.61049517592393</v>
+        <v>22.6105</v>
       </c>
       <c r="G3" t="n">
         <v>3.416844086692463e-113</v>
@@ -506,19 +506,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.2646677082932205</v>
+        <v>-0.2647</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007494751020465687</v>
+        <v>0.0075</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3504497355341742</v>
+        <v>-0.3504</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009923891093305548</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-35.31374258737888</v>
+        <v>-35.3137</v>
       </c>
       <c r="G4" t="n">
         <v>3.613434805884537e-273</v>
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.001193444128414648</v>
+        <v>-0.0012</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0005451496638546373</v>
+        <v>0.0005</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.01767857637219977</v>
+        <v>-0.0177</v>
       </c>
       <c r="E5" t="n">
-        <v>0.008075342395404379</v>
+        <v>0.0081</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.189204557104665</v>
+        <v>-2.1892</v>
       </c>
       <c r="G5" t="n">
         <v>0.02858197558367184</v>
@@ -556,19 +556,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06631146661836736</v>
+        <v>0.0663</v>
       </c>
       <c r="C6" t="n">
-        <v>0.009181824463075267</v>
+        <v>0.0092</v>
       </c>
       <c r="D6" t="n">
-        <v>0.07532570921234086</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01042998254773623</v>
+        <v>0.0104</v>
       </c>
       <c r="F6" t="n">
-        <v>7.22203597825673</v>
+        <v>7.222</v>
       </c>
       <c r="G6" t="n">
         <v>5.121491758353771e-13</v>
@@ -581,19 +581,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.09663618630069984</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009815550098897844</v>
+        <v>0.0098</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1037110872892521</v>
+        <v>0.1037</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01053416336124027</v>
+        <v>0.0105</v>
       </c>
       <c r="F7" t="n">
-        <v>9.845213495629837</v>
+        <v>9.8452</v>
       </c>
       <c r="G7" t="n">
         <v>7.18864398705146e-23</v>
@@ -606,19 +606,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06251063690323681</v>
+        <v>0.0625</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009174040190048265</v>
+        <v>0.0092</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06069865443742067</v>
+        <v>0.0607</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008908114248663411</v>
+        <v>0.0089</v>
       </c>
       <c r="F8" t="n">
-        <v>6.813861244149176</v>
+        <v>6.8139</v>
       </c>
       <c r="G8" t="n">
         <v>9.501335183611905e-12</v>
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.003383484822056926</v>
+        <v>-0.0034</v>
       </c>
       <c r="C9" t="n">
-        <v>0.008361915698620277</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.003170577618155896</v>
+        <v>-0.0032</v>
       </c>
       <c r="E9" t="n">
-        <v>0.007835738640268037</v>
+        <v>0.0078</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4046303435724906</v>
+        <v>-0.4046</v>
       </c>
       <c r="G9" t="n">
         <v>0.6857492507426544</v>
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1400427013417813</v>
+        <v>0.14</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01438273272011647</v>
+        <v>0.0144</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1163016886957703</v>
+        <v>0.1163</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01194447184596259</v>
+        <v>0.0119</v>
       </c>
       <c r="F10" t="n">
-        <v>9.736863228078347</v>
+        <v>9.7369</v>
       </c>
       <c r="G10" t="n">
         <v>2.099345818653748e-22</v>
@@ -681,19 +681,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04398230665684229</v>
+        <v>0.044</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0105618678150626</v>
+        <v>0.0106</v>
       </c>
       <c r="D11" t="n">
-        <v>0.03609493541205414</v>
+        <v>0.0361</v>
       </c>
       <c r="E11" t="n">
-        <v>0.008667802250340367</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>4.164254602213238</v>
+        <v>4.1643</v>
       </c>
       <c r="G11" t="n">
         <v>3.123713916089543e-05</v>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.07355837143582948</v>
+        <v>0.0736</v>
       </c>
       <c r="C12" t="n">
-        <v>0.01133029003350461</v>
+        <v>0.0113</v>
       </c>
       <c r="D12" t="n">
-        <v>0.05411987174455068</v>
+        <v>0.0541</v>
       </c>
       <c r="E12" t="n">
-        <v>0.008336153064192912</v>
+        <v>0.0083</v>
       </c>
       <c r="F12" t="n">
-        <v>6.492187862650582</v>
+        <v>6.4922</v>
       </c>
       <c r="G12" t="n">
         <v>8.459867074906337e-11</v>
@@ -731,19 +731,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05561521477810218</v>
+        <v>0.0556</v>
       </c>
       <c r="C13" t="n">
-        <v>0.01182832483759637</v>
+        <v>0.0118</v>
       </c>
       <c r="D13" t="n">
-        <v>0.03786236654343974</v>
+        <v>0.0379</v>
       </c>
       <c r="E13" t="n">
-        <v>0.008052623232379945</v>
+        <v>0.0081</v>
       </c>
       <c r="F13" t="n">
-        <v>4.701867385424607</v>
+        <v>4.7019</v>
       </c>
       <c r="G13" t="n">
         <v>2.57792917769175e-06</v>
@@ -756,19 +756,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.04024942198362007</v>
+        <v>0.0402</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0121551211910208</v>
+        <v>0.0122</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0253796190931974</v>
+        <v>0.0254</v>
       </c>
       <c r="E14" t="n">
-        <v>0.007664516175792637</v>
+        <v>0.0077</v>
       </c>
       <c r="F14" t="n">
-        <v>3.311313918725304</v>
+        <v>3.3113</v>
       </c>
       <c r="G14" t="n">
         <v>0.0009285897517735443</v>
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.03020017969085996</v>
+        <v>-0.0302</v>
       </c>
       <c r="C15" t="n">
-        <v>0.00998105784781708</v>
+        <v>0.01</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.01785347061943688</v>
+        <v>-0.0179</v>
       </c>
       <c r="E15" t="n">
-        <v>0.005900512012212731</v>
+        <v>0.0059</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.025749389626565</v>
+        <v>-3.0257</v>
       </c>
       <c r="G15" t="n">
         <v>0.002480177768151905</v>
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.001521276948518539</v>
+        <v>-0.0015</v>
       </c>
       <c r="C16" t="n">
-        <v>0.01051982944307036</v>
+        <v>0.0105</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0008694517702159131</v>
+        <v>-0.0009</v>
       </c>
       <c r="E16" t="n">
-        <v>0.006012372921678793</v>
+        <v>0.006</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1446104194703116</v>
+        <v>-0.1446</v>
       </c>
       <c r="G16" t="n">
         <v>0.8850184701674246</v>
@@ -831,19 +831,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1149745132743056</v>
+        <v>0.115</v>
       </c>
       <c r="C17" t="n">
-        <v>0.02359981280812879</v>
+        <v>0.0236</v>
       </c>
       <c r="D17" t="n">
-        <v>0.04534665603895969</v>
+        <v>0.0453</v>
       </c>
       <c r="E17" t="n">
-        <v>0.009307911497227555</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>4.871840052676328</v>
+        <v>4.8718</v>
       </c>
       <c r="G17" t="n">
         <v>1.105636634491079e-06</v>
@@ -856,19 +856,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.06258108346606112</v>
+        <v>-0.0626</v>
       </c>
       <c r="C18" t="n">
-        <v>0.008836144308575725</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0216514854101746</v>
+        <v>-0.0217</v>
       </c>
       <c r="E18" t="n">
-        <v>0.003057084329373726</v>
+        <v>0.0031</v>
       </c>
       <c r="F18" t="n">
-        <v>-7.082397172409738</v>
+        <v>-7.0824</v>
       </c>
       <c r="G18" t="n">
         <v>1.416818879886341e-12</v>
@@ -881,19 +881,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.08625824630920757</v>
+        <v>0.0863</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02523616482623088</v>
+        <v>0.0252</v>
       </c>
       <c r="D19" t="n">
-        <v>0.02502470882421028</v>
+        <v>0.025</v>
       </c>
       <c r="E19" t="n">
-        <v>0.007321360028030076</v>
+        <v>0.0073</v>
       </c>
       <c r="F19" t="n">
-        <v>3.418041009921973</v>
+        <v>3.418</v>
       </c>
       <c r="G19" t="n">
         <v>0.0006307360247045329</v>
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.05652733154884899</v>
+        <v>0.0565</v>
       </c>
       <c r="C20" t="n">
-        <v>0.03079923924048143</v>
+        <v>0.0308</v>
       </c>
       <c r="D20" t="n">
-        <v>0.01136717701512804</v>
+        <v>0.0114</v>
       </c>
       <c r="E20" t="n">
-        <v>0.00619347127814242</v>
+        <v>0.0062</v>
       </c>
       <c r="F20" t="n">
-        <v>1.835348305439684</v>
+        <v>1.8353</v>
       </c>
       <c r="G20" t="n">
         <v>0.06645409798580651</v>
@@ -931,19 +931,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.3081649680877036</v>
+        <v>-0.3082</v>
       </c>
       <c r="C21" t="n">
-        <v>0.04245361604253767</v>
+        <v>0.0425</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.04386480052077236</v>
+        <v>-0.0439</v>
       </c>
       <c r="E21" t="n">
-        <v>0.006042930222235349</v>
+        <v>0.006</v>
       </c>
       <c r="F21" t="n">
-        <v>-7.258862655631702</v>
+        <v>-7.2589</v>
       </c>
       <c r="G21" t="n">
         <v>3.903585811780023e-13</v>
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1311089914432668</v>
+        <v>-0.1311</v>
       </c>
       <c r="C22" t="n">
-        <v>0.006022886358007171</v>
+        <v>0.006</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1742917649144759</v>
+        <v>-0.1743</v>
       </c>
       <c r="E22" t="n">
-        <v>0.008006617102768506</v>
+        <v>0.008</v>
       </c>
       <c r="F22" t="n">
-        <v>-21.76846509298037</v>
+        <v>-21.7685</v>
       </c>
       <c r="G22" t="n">
         <v>4.618387003790065e-105</v>
@@ -981,19 +981,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.1107515140736464</v>
+        <v>-0.1108</v>
       </c>
       <c r="C23" t="n">
-        <v>0.007485696856691884</v>
+        <v>0.0075</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1151570868563532</v>
+        <v>-0.1152</v>
       </c>
       <c r="E23" t="n">
-        <v>0.007783469601446468</v>
+        <v>0.0078</v>
       </c>
       <c r="F23" t="n">
-        <v>-14.79508403745196</v>
+        <v>-14.7951</v>
       </c>
       <c r="G23" t="n">
         <v>1.575873980804803e-49</v>
@@ -1006,19 +1006,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.2372773237589519</v>
+        <v>-0.2373</v>
       </c>
       <c r="C24" t="n">
-        <v>0.009452746660971361</v>
+        <v>0.0095</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1722802254946329</v>
+        <v>-0.1723</v>
       </c>
       <c r="E24" t="n">
-        <v>0.006863366884355901</v>
+        <v>0.0069</v>
       </c>
       <c r="F24" t="n">
-        <v>-25.10141573333664</v>
+        <v>-25.1014</v>
       </c>
       <c r="G24" t="n">
         <v>4.799422352546218e-139</v>
@@ -1031,19 +1031,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.04320650554590563</v>
+        <v>-0.0432</v>
       </c>
       <c r="C25" t="n">
-        <v>0.008266537090080094</v>
+        <v>0.0083</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.04992295848619177</v>
+        <v>-0.0499</v>
       </c>
       <c r="E25" t="n">
-        <v>0.009551570597028778</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.22667533878893</v>
+        <v>-5.2267</v>
       </c>
       <c r="G25" t="n">
         <v>1.725851529309045e-07</v>
@@ -1056,19 +1056,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1595856016157796</v>
+        <v>-0.1596</v>
       </c>
       <c r="C26" t="n">
-        <v>0.006430429664423285</v>
+        <v>0.0064</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1613499190370889</v>
+        <v>-0.1613</v>
       </c>
       <c r="E26" t="n">
-        <v>0.006501522037222436</v>
+        <v>0.0065</v>
       </c>
       <c r="F26" t="n">
-        <v>-24.81725326982363</v>
+        <v>-24.8173</v>
       </c>
       <c r="G26" t="n">
         <v>5.839207849537465e-136</v>

--- a/output/coefficients/standardized/standardized_OVR.xlsx
+++ b/output/coefficients/standardized/standardized_OVR.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4783</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="C2" t="n">
         <v>0.0103</v>
@@ -468,7 +468,7 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>46.4039</v>
+        <v>49.3949</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -481,22 +481,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1115</v>
+        <v>0.1076</v>
       </c>
       <c r="C3" t="n">
         <v>0.0049</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2412</v>
+        <v>0.2328</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0107</v>
+        <v>0.0106</v>
       </c>
       <c r="F3" t="n">
-        <v>22.6105</v>
+        <v>21.9733</v>
       </c>
       <c r="G3" t="n">
-        <v>3.416844086692463e-113</v>
+        <v>5.19024484586208e-107</v>
       </c>
     </row>
     <row r="4">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.2647</v>
+        <v>-0.2455</v>
       </c>
       <c r="C4" t="n">
         <v>0.0075</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3504</v>
+        <v>-0.3251</v>
       </c>
       <c r="E4" t="n">
         <v>0.009900000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-35.3137</v>
+        <v>-32.7927</v>
       </c>
       <c r="G4" t="n">
-        <v>3.613434805884537e-273</v>
+        <v>7.492269383312129e-236</v>
       </c>
     </row>
     <row r="5">
@@ -531,22 +531,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.0012</v>
+        <v>-0.0015</v>
       </c>
       <c r="C5" t="n">
         <v>0.0005</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0177</v>
+        <v>-0.022</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0081</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.1892</v>
+        <v>-2.768</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02858197558367184</v>
+        <v>0.005640304136887425</v>
       </c>
     </row>
     <row r="6">
@@ -556,22 +556,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0663</v>
+        <v>0.0529</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0092</v>
+        <v>0.0091</v>
       </c>
       <c r="D6" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.0601</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0104</v>
+        <v>0.0103</v>
       </c>
       <c r="F6" t="n">
-        <v>7.222</v>
+        <v>5.8113</v>
       </c>
       <c r="G6" t="n">
-        <v>5.121491758353771e-13</v>
+        <v>6.199053613937379e-09</v>
       </c>
     </row>
     <row r="7">
@@ -581,22 +581,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.0706</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0098</v>
+        <v>0.0097</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1037</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0105</v>
+        <v>0.0104</v>
       </c>
       <c r="F7" t="n">
-        <v>9.8452</v>
+        <v>7.2972</v>
       </c>
       <c r="G7" t="n">
-        <v>7.18864398705146e-23</v>
+        <v>2.937960448986889e-13</v>
       </c>
     </row>
     <row r="8">
@@ -606,22 +606,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0625</v>
+        <v>0.0592</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0092</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0607</v>
+        <v>0.0574</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0089</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>6.8139</v>
+        <v>6.5405</v>
       </c>
       <c r="G8" t="n">
-        <v>9.501335183611905e-12</v>
+        <v>6.129438846606865e-11</v>
       </c>
     </row>
     <row r="9">
@@ -631,22 +631,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.0034</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0032</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0078</v>
+        <v>0.0077</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4046</v>
+        <v>1.2043</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6857492507426544</v>
+        <v>0.2284826860528429</v>
       </c>
     </row>
     <row r="10">
@@ -656,22 +656,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.14</v>
+        <v>0.1313</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0144</v>
+        <v>0.014</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1163</v>
+        <v>0.109</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0119</v>
+        <v>0.0116</v>
       </c>
       <c r="F10" t="n">
-        <v>9.7369</v>
+        <v>9.3592</v>
       </c>
       <c r="G10" t="n">
-        <v>2.099345818653748e-22</v>
+        <v>8.034314722850815e-21</v>
       </c>
     </row>
     <row r="11">
@@ -681,22 +681,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.044</v>
+        <v>0.0449</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0106</v>
+        <v>0.0104</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0361</v>
+        <v>0.0368</v>
       </c>
       <c r="E11" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>4.1643</v>
+        <v>4.3228</v>
       </c>
       <c r="G11" t="n">
-        <v>3.123713916089543e-05</v>
+        <v>1.54082537388473e-05</v>
       </c>
     </row>
     <row r="12">
@@ -706,22 +706,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0736</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0113</v>
+        <v>0.011</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0541</v>
+        <v>0.0473</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0083</v>
+        <v>0.0081</v>
       </c>
       <c r="F12" t="n">
-        <v>6.4922</v>
+        <v>5.8224</v>
       </c>
       <c r="G12" t="n">
-        <v>8.459867074906337e-11</v>
+        <v>5.801343260495562e-09</v>
       </c>
     </row>
     <row r="13">
@@ -731,22 +731,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0556</v>
+        <v>0.0434</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0118</v>
+        <v>0.0116</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0379</v>
+        <v>0.0295</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0081</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>4.7019</v>
+        <v>3.7416</v>
       </c>
       <c r="G13" t="n">
-        <v>2.57792917769175e-06</v>
+        <v>0.0001828608945014619</v>
       </c>
     </row>
     <row r="14">
@@ -756,22 +756,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0402</v>
+        <v>0.0347</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0122</v>
+        <v>0.012</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0254</v>
+        <v>0.0219</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0077</v>
+        <v>0.0075</v>
       </c>
       <c r="F14" t="n">
-        <v>3.3113</v>
+        <v>2.9029</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0009285897517735443</v>
+        <v>0.003697766179605234</v>
       </c>
     </row>
     <row r="15">
@@ -781,22 +781,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.0302</v>
+        <v>-0.0391</v>
       </c>
       <c r="C15" t="n">
-        <v>0.01</v>
+        <v>0.0098</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0179</v>
+        <v>-0.0231</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0059</v>
+        <v>0.0058</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.0257</v>
+        <v>-3.9877</v>
       </c>
       <c r="G15" t="n">
-        <v>0.002480177768151905</v>
+        <v>6.671685620093757e-05</v>
       </c>
     </row>
     <row r="16">
@@ -806,22 +806,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.0015</v>
+        <v>0.0118</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0105</v>
+        <v>0.0106</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0009</v>
+        <v>0.0068</v>
       </c>
       <c r="E16" t="n">
         <v>0.006</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1446</v>
+        <v>1.1205</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8850184701674246</v>
+        <v>0.2625053442913986</v>
       </c>
     </row>
     <row r="17">
@@ -831,22 +831,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.115</v>
+        <v>0.0912</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0236</v>
+        <v>0.0232</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0453</v>
+        <v>0.036</v>
       </c>
       <c r="E17" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0091</v>
       </c>
       <c r="F17" t="n">
-        <v>4.8718</v>
+        <v>3.9356</v>
       </c>
       <c r="G17" t="n">
-        <v>1.105636634491079e-06</v>
+        <v>8.297693984728184e-05</v>
       </c>
     </row>
     <row r="18">
@@ -856,22 +856,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.0626</v>
+        <v>-0.0266</v>
       </c>
       <c r="C18" t="n">
         <v>0.008800000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0217</v>
+        <v>-0.0092</v>
       </c>
       <c r="E18" t="n">
         <v>0.0031</v>
       </c>
       <c r="F18" t="n">
-        <v>-7.0824</v>
+        <v>-3.016</v>
       </c>
       <c r="G18" t="n">
-        <v>1.416818879886341e-12</v>
+        <v>0.002561019149257387</v>
       </c>
     </row>
     <row r="19">
@@ -881,22 +881,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0863</v>
+        <v>0.0602</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0252</v>
+        <v>0.0246</v>
       </c>
       <c r="D19" t="n">
-        <v>0.025</v>
+        <v>0.0175</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0073</v>
+        <v>0.0071</v>
       </c>
       <c r="F19" t="n">
-        <v>3.418</v>
+        <v>2.4446</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0006307360247045329</v>
+        <v>0.01450079799139041</v>
       </c>
     </row>
     <row r="20">
@@ -906,22 +906,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.0565</v>
+        <v>0.0165</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0308</v>
+        <v>0.0309</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0114</v>
+        <v>0.0033</v>
       </c>
       <c r="E20" t="n">
         <v>0.0062</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8353</v>
+        <v>0.5346</v>
       </c>
       <c r="G20" t="n">
-        <v>0.06645409798580651</v>
+        <v>0.5928969351046378</v>
       </c>
     </row>
     <row r="21">
@@ -931,22 +931,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.3082</v>
+        <v>-0.3222</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0425</v>
+        <v>0.043</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0439</v>
+        <v>-0.0459</v>
       </c>
       <c r="E21" t="n">
-        <v>0.006</v>
+        <v>0.0061</v>
       </c>
       <c r="F21" t="n">
-        <v>-7.2589</v>
+        <v>-7.4914</v>
       </c>
       <c r="G21" t="n">
-        <v>3.903585811780023e-13</v>
+        <v>6.812353441902274e-14</v>
       </c>
     </row>
     <row r="22">
@@ -956,22 +956,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1311</v>
+        <v>-0.1202</v>
       </c>
       <c r="C22" t="n">
-        <v>0.006</v>
+        <v>0.0059</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1743</v>
+        <v>-0.1597</v>
       </c>
       <c r="E22" t="n">
-        <v>0.008</v>
+        <v>0.0078</v>
       </c>
       <c r="F22" t="n">
-        <v>-21.7685</v>
+        <v>-20.4092</v>
       </c>
       <c r="G22" t="n">
-        <v>4.618387003790065e-105</v>
+        <v>1.385639557257553e-92</v>
       </c>
     </row>
     <row r="23">
@@ -981,22 +981,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.1108</v>
+        <v>-0.1018</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0075</v>
+        <v>0.0074</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1152</v>
+        <v>-0.1059</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0078</v>
+        <v>0.0076</v>
       </c>
       <c r="F23" t="n">
-        <v>-14.7951</v>
+        <v>-13.8522</v>
       </c>
       <c r="G23" t="n">
-        <v>1.575873980804803e-49</v>
+        <v>1.233771683303811e-43</v>
       </c>
     </row>
     <row r="24">
@@ -1006,22 +1006,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.2373</v>
+        <v>-0.2341</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0095</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1723</v>
+        <v>-0.1699</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0069</v>
+        <v>0.0068</v>
       </c>
       <c r="F24" t="n">
-        <v>-25.1014</v>
+        <v>-25.0389</v>
       </c>
       <c r="G24" t="n">
-        <v>4.799422352546218e-139</v>
+        <v>2.307580081083772e-138</v>
       </c>
     </row>
     <row r="25">
@@ -1031,22 +1031,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.0432</v>
+        <v>-0.0467</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0083</v>
+        <v>0.0081</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0499</v>
+        <v>-0.0539</v>
       </c>
       <c r="E25" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0094</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.2267</v>
+        <v>-5.7408</v>
       </c>
       <c r="G25" t="n">
-        <v>1.725851529309045e-07</v>
+        <v>9.422985697115229e-09</v>
       </c>
     </row>
     <row r="26">
@@ -1056,22 +1056,97 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1596</v>
+        <v>-0.1491</v>
       </c>
       <c r="C26" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.1507</v>
+      </c>
+      <c r="E26" t="n">
         <v>0.0064</v>
       </c>
-      <c r="D26" t="n">
-        <v>-0.1613</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.0065</v>
-      </c>
       <c r="F26" t="n">
-        <v>-24.8173</v>
+        <v>-23.6238</v>
       </c>
       <c r="G26" t="n">
-        <v>5.839207849537465e-136</v>
+        <v>2.196787974340853e-123</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>d_aa</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-0.08890000000000001</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.1091</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-17.0953</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.609484180381554e-65</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>d_indie</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>-0.065</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.0611</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-9.814500000000001</v>
+      </c>
+      <c r="G28" t="n">
+        <v>9.7508750172815e-23</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>d_unknown</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>-0.1334</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-0.1503</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.0053</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-28.5691</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.627152312090757e-179</v>
       </c>
     </row>
   </sheetData>
